--- a/events/Gualeguaychu_2026_MAR/Gualeguaychu_2026_MAR_Results.xlsx
+++ b/events/Gualeguaychu_2026_MAR/Gualeguaychu_2026_MAR_Results.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -581,7 +580,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -653,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -725,7 +724,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -797,7 +796,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -869,7 +868,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -941,7 +940,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1013,7 +1012,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1085,7 +1084,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1157,7 +1156,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1229,7 +1228,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1301,7 +1300,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1373,7 +1372,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1445,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1517,7 +1516,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1589,7 +1588,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1661,7 +1660,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1733,7 +1732,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1805,7 +1804,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1877,7 +1876,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1949,7 +1948,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2021,7 +2020,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2093,7 +2092,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2165,7 +2164,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2237,7 +2236,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2309,7 +2308,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2381,7 +2380,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2453,7 +2452,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2525,7 +2524,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2597,7 +2596,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2669,7 +2668,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2741,7 +2740,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2813,7 +2812,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2885,7 +2884,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2957,7 +2956,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3029,7 +3028,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3101,7 +3100,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3173,7 +3172,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3245,7 +3244,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3317,7 +3316,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3389,7 +3388,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3461,7 +3460,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3533,7 +3532,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3605,7 +3604,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3677,7 +3676,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3749,7 +3748,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3821,7 +3820,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3893,7 +3892,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3965,7 +3964,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4037,7 +4036,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4109,7 +4108,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4181,7 +4180,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4253,7 +4252,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4325,7 +4324,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4397,7 +4396,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4469,7 +4468,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4541,7 +4540,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4613,7 +4612,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4685,7 +4684,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4757,7 +4756,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4829,7 +4828,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4901,7 +4900,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4973,7 +4972,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5045,7 +5044,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5117,7 +5116,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5189,7 +5188,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5261,7 +5260,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5333,7 +5332,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5405,7 +5404,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5477,7 +5476,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5549,7 +5548,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5621,7 +5620,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5693,7 +5692,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5765,7 +5764,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5837,7 +5836,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5909,7 +5908,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5981,7 +5980,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6053,7 +6052,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6125,7 +6124,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6197,7 +6196,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6269,7 +6268,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6341,7 +6340,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6413,7 +6412,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6485,7 +6484,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6557,7 +6556,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6626,7 +6625,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6698,7 +6697,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6770,7 +6769,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6842,7 +6841,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6914,7 +6913,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6986,7 +6985,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7058,7 +7057,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7130,7 +7129,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7202,7 +7201,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7274,7 +7273,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7346,7 +7345,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7418,7 +7417,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7490,7 +7489,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7562,7 +7561,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7634,7 +7633,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7706,7 +7705,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7778,7 +7777,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7850,7 +7849,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7922,7 +7921,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7994,7 +7993,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8066,7 +8065,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8138,7 +8137,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8210,7 +8209,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8282,7 +8281,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8354,7 +8353,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8426,7 +8425,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8498,7 +8497,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8570,7 +8569,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8642,7 +8641,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8714,7 +8713,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8783,7 +8782,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8855,7 +8854,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8927,7 +8926,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8999,7 +8998,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -9071,7 +9070,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9143,7 +9142,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9215,7 +9214,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9287,7 +9286,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9359,7 +9358,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9431,7 +9430,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9503,7 +9502,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9575,7 +9574,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9647,7 +9646,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9719,7 +9718,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9791,7 +9790,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -9863,7 +9862,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -9935,7 +9934,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10007,7 +10006,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10079,7 +10078,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -10151,7 +10150,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -10223,7 +10222,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -10295,7 +10294,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -10367,7 +10366,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -10439,7 +10438,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -10511,7 +10510,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -10583,7 +10582,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -10655,7 +10654,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -10727,7 +10726,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -10799,7 +10798,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -10871,7 +10870,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -10943,7 +10942,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -11015,7 +11014,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -11087,7 +11086,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -11159,7 +11158,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -11231,7 +11230,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -11303,7 +11302,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -11375,7 +11374,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11447,7 +11446,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11519,7 +11518,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11591,7 +11590,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11663,7 +11662,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11735,7 +11734,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11807,7 +11806,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11879,7 +11878,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11951,7 +11950,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -12023,7 +12022,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -12095,7 +12094,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -12167,7 +12166,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -12239,7 +12238,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -12311,7 +12310,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -12383,7 +12382,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -12455,7 +12454,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -12527,7 +12526,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12599,7 +12598,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -12671,7 +12670,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -12743,7 +12742,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -12812,7 +12811,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -12884,7 +12883,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -12956,7 +12955,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -13028,7 +13027,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -13100,7 +13099,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -13172,7 +13171,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -13244,7 +13243,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -13316,7 +13315,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -13388,7 +13387,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -13460,7 +13459,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -13532,7 +13531,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -13601,7 +13600,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -13670,7 +13669,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -13739,7 +13738,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -13811,7 +13810,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -13883,7 +13882,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -13955,7 +13954,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -14027,7 +14026,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -14099,7 +14098,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -14171,7 +14170,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -14243,7 +14242,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -14315,7 +14314,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -14387,7 +14386,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -14459,7 +14458,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -14531,7 +14530,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -14603,7 +14602,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -14675,7 +14674,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -14747,7 +14746,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -14819,7 +14818,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -14891,7 +14890,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -14963,7 +14962,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15035,7 +15034,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -15104,7 +15103,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -15173,7 +15172,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -15245,7 +15244,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -15317,7 +15316,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -15389,7 +15388,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -15461,7 +15460,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -15533,7 +15532,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -15605,7 +15604,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -15677,7 +15676,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -15749,7 +15748,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -15821,7 +15820,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -15893,7 +15892,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -15965,7 +15964,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -16037,7 +16036,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -16109,7 +16108,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -16181,7 +16180,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -16253,7 +16252,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -16325,7 +16324,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -16397,7 +16396,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -16469,7 +16468,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -16541,7 +16540,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -16613,7 +16612,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -16685,7 +16684,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -16757,7 +16756,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -16829,7 +16828,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -16901,7 +16900,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -16973,7 +16972,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -17045,7 +17044,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -17117,7 +17116,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -17189,7 +17188,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -17261,7 +17260,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -17333,7 +17332,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -17405,7 +17404,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -17477,7 +17476,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -17549,7 +17548,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -17621,7 +17620,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -17693,7 +17692,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -17765,7 +17764,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -17837,7 +17836,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -17909,7 +17908,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -17981,7 +17980,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -18053,7 +18052,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -18125,7 +18124,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -18197,7 +18196,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -18269,7 +18268,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -18341,7 +18340,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -18413,7 +18412,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -18485,7 +18484,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -18557,7 +18556,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -18629,7 +18628,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -18701,7 +18700,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -18773,7 +18772,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -18845,7 +18844,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -18917,7 +18916,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -18989,7 +18988,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -19061,7 +19060,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -19133,7 +19132,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -19205,7 +19204,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -19274,7 +19273,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -19346,7 +19345,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -19418,7 +19417,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -19490,7 +19489,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -19562,7 +19561,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -19634,7 +19633,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -19706,7 +19705,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -19778,7 +19777,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -19850,7 +19849,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -19922,7 +19921,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -19994,7 +19993,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -20066,7 +20065,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -20138,7 +20137,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -20210,7 +20209,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -20282,7 +20281,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -20354,7 +20353,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -20426,7 +20425,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -20498,7 +20497,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -20570,7 +20569,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -20642,7 +20641,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -20714,7 +20713,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -20786,7 +20785,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -20858,7 +20857,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -20927,7 +20926,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -20999,7 +20998,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -21071,7 +21070,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -21143,7 +21142,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -21215,7 +21214,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -21287,7 +21286,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -21359,7 +21358,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -21431,7 +21430,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -21503,7 +21502,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -21575,7 +21574,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -21647,7 +21646,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -21719,7 +21718,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -21791,7 +21790,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -21863,7 +21862,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -21935,7 +21934,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -22007,7 +22006,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -22079,7 +22078,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -22151,7 +22150,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -22223,7 +22222,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -22295,7 +22294,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -22367,7 +22366,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -22439,7 +22438,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -22511,7 +22510,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -22583,7 +22582,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -22655,7 +22654,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -22727,7 +22726,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -22799,7 +22798,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -22871,7 +22870,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -22943,7 +22942,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -23015,7 +23014,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -23087,7 +23086,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -23159,7 +23158,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -23231,7 +23230,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -23303,7 +23302,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -23375,7 +23374,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -23447,7 +23446,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -23519,7 +23518,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -23591,7 +23590,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -23663,7 +23662,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -23735,7 +23734,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -23807,7 +23806,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -23879,7 +23878,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -23951,7 +23950,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -24023,7 +24022,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -24095,7 +24094,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -24167,7 +24166,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -24239,7 +24238,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -24311,7 +24310,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -24380,7 +24379,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -24452,7 +24451,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -24524,7 +24523,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -24596,7 +24595,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -24668,7 +24667,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -24740,7 +24739,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -24812,7 +24811,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -24884,7 +24883,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -24956,7 +24955,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -25028,7 +25027,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -25100,7 +25099,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -25172,7 +25171,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -25244,7 +25243,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -25316,7 +25315,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -25388,7 +25387,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -25460,7 +25459,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -25532,7 +25531,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -25604,7 +25603,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -25676,7 +25675,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -25748,7 +25747,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -25820,7 +25819,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -25892,7 +25891,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -25964,7 +25963,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -26033,7 +26032,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -26102,7 +26101,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -26174,7 +26173,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -26246,7 +26245,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -26318,7 +26317,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -26390,7 +26389,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -26462,7 +26461,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -26534,7 +26533,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -26606,7 +26605,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -26678,7 +26677,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -26750,7 +26749,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -26822,7 +26821,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -26891,7 +26890,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -26960,7 +26959,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -27037,7 +27036,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -27114,7 +27113,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -27191,7 +27190,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -27268,7 +27267,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -27345,7 +27344,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -27422,7 +27421,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -27496,7 +27495,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -27568,7 +27567,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -27640,7 +27639,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -27712,7 +27711,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -27784,7 +27783,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -27856,7 +27855,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -27928,7 +27927,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -28000,7 +27999,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -28072,7 +28071,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -28144,7 +28143,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -28216,7 +28215,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -28288,7 +28287,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -28360,7 +28359,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -28432,7 +28431,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -28504,7 +28503,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -28576,7 +28575,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -28648,7 +28647,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -28720,7 +28719,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -28792,7 +28791,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -28864,7 +28863,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -28936,7 +28935,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -29008,7 +29007,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -29080,7 +29079,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -29152,7 +29151,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -29224,7 +29223,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -29296,7 +29295,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -29368,7 +29367,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -29440,7 +29439,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -29509,7 +29508,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -29578,7 +29577,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -29650,7 +29649,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -29722,7 +29721,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -29794,7 +29793,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -29866,7 +29865,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -29938,7 +29937,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -30010,7 +30009,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -30082,7 +30081,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -30154,7 +30153,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -30226,7 +30225,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -30298,7 +30297,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -30370,7 +30369,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -30442,7 +30441,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -30514,7 +30513,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -30586,7 +30585,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -30658,7 +30657,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -30730,7 +30729,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -30802,7 +30801,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -30874,7 +30873,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -30946,7 +30945,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -31018,7 +31017,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -31090,7 +31089,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -31162,7 +31161,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -31234,7 +31233,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -31306,7 +31305,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -31378,7 +31377,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -31450,7 +31449,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -31522,7 +31521,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -31591,7 +31590,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -31660,7 +31659,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -31737,7 +31736,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -31814,7 +31813,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -31891,7 +31890,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -31968,7 +31967,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -32045,7 +32044,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -32122,7 +32121,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -32199,7 +32198,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -32276,7 +32275,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -32353,7 +32352,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -32430,7 +32429,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -32507,7 +32506,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -32584,7 +32583,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -32658,7 +32657,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -32730,7 +32729,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -32802,7 +32801,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -32874,7 +32873,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -32946,7 +32945,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -33018,7 +33017,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -33090,7 +33089,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -33162,7 +33161,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -33234,7 +33233,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -33306,7 +33305,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -33378,7 +33377,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -33450,7 +33449,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -33522,7 +33521,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -33594,7 +33593,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -33666,7 +33665,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -33738,7 +33737,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -33810,7 +33809,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -33882,7 +33881,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -33954,7 +33953,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -34026,7 +34025,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -34098,7 +34097,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -34170,7 +34169,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -34242,7 +34241,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -34311,7 +34310,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -34380,7 +34379,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -34452,7 +34451,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -34524,7 +34523,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -34596,7 +34595,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -34668,7 +34667,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -34740,7 +34739,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -34812,7 +34811,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -34884,7 +34883,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -34956,7 +34955,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -35028,7 +35027,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -35100,7 +35099,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -35172,7 +35171,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -35244,7 +35243,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -35316,7 +35315,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -35388,7 +35387,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -35460,7 +35459,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -35532,7 +35531,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -35604,7 +35603,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -35676,7 +35675,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -35748,7 +35747,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -35820,7 +35819,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -35892,7 +35891,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -35964,7 +35963,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -36036,7 +36035,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -36108,7 +36107,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -36180,7 +36179,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -36252,7 +36251,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -36324,7 +36323,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -36396,7 +36395,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -36468,7 +36467,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -36540,7 +36539,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -36612,7 +36611,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -36681,7 +36680,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -36750,7 +36749,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -36819,7 +36818,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -36891,7 +36890,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -36963,7 +36962,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -37035,7 +37034,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -37107,7 +37106,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -37179,7 +37178,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -37251,7 +37250,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -37323,7 +37322,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -37395,7 +37394,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -37467,7 +37466,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -37539,7 +37538,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -37608,7 +37607,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -37677,7 +37676,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -37746,7 +37745,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -37818,7 +37817,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -37890,7 +37889,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -37962,7 +37961,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
@@ -38034,7 +38033,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -38106,7 +38105,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -38178,7 +38177,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -38250,7 +38249,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -38322,7 +38321,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -38394,7 +38393,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
@@ -38466,7 +38465,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -38538,7 +38537,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -38610,7 +38609,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -38682,7 +38681,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -38754,7 +38753,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
@@ -38826,7 +38825,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
@@ -38898,7 +38897,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -38970,7 +38969,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
@@ -39042,7 +39041,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -39114,7 +39113,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -39186,7 +39185,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -39258,7 +39257,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -39330,7 +39329,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
@@ -39402,7 +39401,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
@@ -39474,7 +39473,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
@@ -39543,7 +39542,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
@@ -39612,7 +39611,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -39681,7 +39680,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
@@ -39750,7 +39749,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
@@ -39819,7 +39818,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -39888,7 +39887,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
@@ -39957,7 +39956,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
@@ -40021,7 +40020,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
@@ -40085,7 +40084,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
@@ -40149,7 +40148,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
@@ -40213,7 +40212,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
@@ -40277,7 +40276,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
@@ -40341,7 +40340,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
@@ -40405,7 +40404,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
@@ -40469,7 +40468,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -40533,7 +40532,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
@@ -40602,7 +40601,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
@@ -40671,7 +40670,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
@@ -40740,7 +40739,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
@@ -40809,7 +40808,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
@@ -40878,7 +40877,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
@@ -40947,7 +40946,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
@@ -41016,7 +41015,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
@@ -41085,7 +41084,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -41154,7 +41153,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -41223,7 +41222,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
@@ -41292,7 +41291,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
@@ -41361,7 +41360,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -41430,7 +41429,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -41499,7 +41498,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
@@ -41568,7 +41567,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -41637,7 +41636,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
@@ -41706,7 +41705,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -41775,7 +41774,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -41844,7 +41843,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
@@ -41913,7 +41912,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
@@ -41982,7 +41981,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
@@ -42051,7 +42050,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -42120,7 +42119,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -42189,7 +42188,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -42258,7 +42257,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
@@ -42327,7 +42326,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
@@ -42396,7 +42395,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -42465,7 +42464,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
@@ -42534,7 +42533,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
@@ -42603,7 +42602,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
@@ -42672,7 +42671,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
@@ -42741,7 +42740,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
@@ -42810,7 +42809,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
@@ -42879,7 +42878,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
@@ -42948,7 +42947,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
@@ -43017,7 +43016,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
@@ -43086,7 +43085,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
@@ -43155,7 +43154,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
@@ -43224,7 +43223,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -43293,7 +43292,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
@@ -43362,7 +43361,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
@@ -43431,7 +43430,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
@@ -43500,7 +43499,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
@@ -43569,7 +43568,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
@@ -43638,7 +43637,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
@@ -43707,7 +43706,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
@@ -43776,7 +43775,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
@@ -43845,7 +43844,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
@@ -43914,7 +43913,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
@@ -43983,7 +43982,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
@@ -44052,7 +44051,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
@@ -44121,7 +44120,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
@@ -44190,7 +44189,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
@@ -44259,7 +44258,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -44328,7 +44327,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
@@ -44397,7 +44396,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
@@ -44466,7 +44465,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
@@ -44535,7 +44534,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
@@ -44604,7 +44603,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
@@ -44673,7 +44672,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
@@ -44742,7 +44741,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>final</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">

--- a/events/Gualeguaychu_2026_MAR/Gualeguaychu_2026_MAR_Results.xlsx
+++ b/events/Gualeguaychu_2026_MAR/Gualeguaychu_2026_MAR_Results.xlsx
@@ -14188,26 +14188,26 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="K191" t="n">
         <v>18</v>
       </c>
       <c r="L191" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M191" t="n">
         <v>7</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>00:14:07.500</t>
+          <t>00:14:06.020</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>136340</t>
+          <t>148776</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -14260,26 +14260,26 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="K192" t="n">
         <v>18</v>
       </c>
       <c r="L192" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M192" t="n">
         <v>8</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>00:14:06.020</t>
+          <t>00:14:07.500</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>148776</t>
+          <t>136340</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -39974,18 +39974,26 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="K549" t="n">
         <v>42</v>
       </c>
       <c r="L549" t="n">
-        <v>606</v>
+        <v>607</v>
+      </c>
+      <c r="M549" t="n">
+        <v>1</v>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>01:17:56.930</t>
+        </is>
       </c>
       <c r="R549" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="Y549" t="inlineStr">
@@ -40038,18 +40046,26 @@
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K550" t="n">
         <v>42</v>
       </c>
       <c r="L550" t="n">
-        <v>607</v>
+        <v>606</v>
+      </c>
+      <c r="M550" t="n">
+        <v>2</v>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>01:20:10.010</t>
+        </is>
       </c>
       <c r="R550" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>105061</t>
         </is>
       </c>
       <c r="Y550" t="inlineStr">
@@ -40102,18 +40118,26 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="K551" t="n">
         <v>42</v>
       </c>
       <c r="L551" t="n">
-        <v>608</v>
+        <v>610</v>
+      </c>
+      <c r="M551" t="n">
+        <v>3</v>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>01:20:18.950</t>
+        </is>
       </c>
       <c r="R551" t="inlineStr">
         <is>
-          <t>63478</t>
+          <t>53283</t>
         </is>
       </c>
       <c r="Y551" t="inlineStr">
@@ -40166,18 +40190,26 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="K552" t="n">
         <v>42</v>
       </c>
       <c r="L552" t="n">
-        <v>609</v>
+        <v>612</v>
+      </c>
+      <c r="M552" t="n">
+        <v>4</v>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>01:20:40.850</t>
+        </is>
       </c>
       <c r="R552" t="inlineStr">
         <is>
-          <t>75589</t>
+          <t>61121</t>
         </is>
       </c>
       <c r="Y552" t="inlineStr">
@@ -40230,18 +40262,26 @@
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K553" t="n">
         <v>42</v>
       </c>
       <c r="L553" t="n">
-        <v>610</v>
+        <v>614</v>
+      </c>
+      <c r="M553" t="n">
+        <v>5</v>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>01:23:08.920</t>
+        </is>
       </c>
       <c r="R553" t="inlineStr">
         <is>
-          <t>53283</t>
+          <t>71701</t>
         </is>
       </c>
       <c r="Y553" t="inlineStr">
@@ -40294,18 +40334,26 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K554" t="n">
         <v>42</v>
       </c>
       <c r="L554" t="n">
-        <v>611</v>
+        <v>608</v>
+      </c>
+      <c r="M554" t="n">
+        <v>6</v>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>01:24:44.550</t>
+        </is>
       </c>
       <c r="R554" t="inlineStr">
         <is>
-          <t>137795</t>
+          <t>63478</t>
         </is>
       </c>
       <c r="Y554" t="inlineStr">
@@ -40358,18 +40406,26 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="K555" t="n">
         <v>42</v>
       </c>
       <c r="L555" t="n">
-        <v>612</v>
+        <v>609</v>
+      </c>
+      <c r="M555" t="n">
+        <v>7</v>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>01:31:27.490</t>
+        </is>
       </c>
       <c r="R555" t="inlineStr">
         <is>
-          <t>61121</t>
+          <t>75589</t>
         </is>
       </c>
       <c r="Y555" t="inlineStr">
@@ -40422,18 +40478,23 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="K556" t="n">
         <v>42</v>
       </c>
       <c r="L556" t="n">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="R556" t="inlineStr">
         <is>
-          <t>122917</t>
+          <t>137795</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
       <c r="Y556" t="inlineStr">
@@ -40486,18 +40547,23 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="K557" t="n">
         <v>42</v>
       </c>
       <c r="L557" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="R557" t="inlineStr">
         <is>
-          <t>71701</t>
+          <t>122917</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
       <c r="Y557" t="inlineStr">
@@ -40550,23 +40616,31 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K558" t="n">
         <v>43</v>
       </c>
       <c r="L558" t="n">
-        <v>616</v>
+        <v>619</v>
+      </c>
+      <c r="M558" t="n">
+        <v>1</v>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>01:55:12.600</t>
+        </is>
       </c>
       <c r="R558" t="inlineStr">
         <is>
-          <t>120955</t>
+          <t>46840</t>
         </is>
       </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>85124</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="Y558" t="inlineStr">
@@ -40619,23 +40693,31 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K559" t="n">
         <v>43</v>
       </c>
       <c r="L559" t="n">
-        <v>617</v>
+        <v>623</v>
+      </c>
+      <c r="M559" t="n">
+        <v>2</v>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>01:55:13.690</t>
+        </is>
       </c>
       <c r="R559" t="inlineStr">
         <is>
-          <t>87162</t>
+          <t>94211</t>
         </is>
       </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>133092</t>
+          <t>98352</t>
         </is>
       </c>
       <c r="Y559" t="inlineStr">
@@ -40688,23 +40770,31 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>RSA</t>
         </is>
       </c>
       <c r="K560" t="n">
         <v>43</v>
       </c>
       <c r="L560" t="n">
-        <v>618</v>
+        <v>620</v>
+      </c>
+      <c r="M560" t="n">
+        <v>3</v>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>01:56:18.660</t>
+        </is>
       </c>
       <c r="R560" t="inlineStr">
         <is>
-          <t>53048</t>
+          <t>134182</t>
         </is>
       </c>
       <c r="S560" t="inlineStr">
         <is>
-          <t>69230</t>
+          <t>111725</t>
         </is>
       </c>
       <c r="Y560" t="inlineStr">
@@ -40764,16 +40854,24 @@
         <v>43</v>
       </c>
       <c r="L561" t="n">
-        <v>619</v>
+        <v>622</v>
+      </c>
+      <c r="M561" t="n">
+        <v>4</v>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>01:56:29.740</t>
+        </is>
       </c>
       <c r="R561" t="inlineStr">
         <is>
-          <t>46840</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="S561" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>123327</t>
         </is>
       </c>
       <c r="Y561" t="inlineStr">
@@ -40826,23 +40924,31 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="K562" t="n">
         <v>43</v>
       </c>
       <c r="L562" t="n">
-        <v>620</v>
+        <v>625</v>
+      </c>
+      <c r="M562" t="n">
+        <v>5</v>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>01:56:35.000</t>
+        </is>
       </c>
       <c r="R562" t="inlineStr">
         <is>
-          <t>134182</t>
+          <t>64233</t>
         </is>
       </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>111725</t>
+          <t>128608</t>
         </is>
       </c>
       <c r="Y562" t="inlineStr">
@@ -40902,16 +41008,24 @@
         <v>43</v>
       </c>
       <c r="L563" t="n">
-        <v>621</v>
+        <v>618</v>
+      </c>
+      <c r="M563" t="n">
+        <v>6</v>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>01:56:46.440</t>
+        </is>
       </c>
       <c r="R563" t="inlineStr">
         <is>
-          <t>128714</t>
+          <t>53048</t>
         </is>
       </c>
       <c r="S563" t="inlineStr">
         <is>
-          <t>88900</t>
+          <t>69230</t>
         </is>
       </c>
       <c r="Y563" t="inlineStr">
@@ -40964,23 +41078,31 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="K564" t="n">
         <v>43</v>
       </c>
       <c r="L564" t="n">
-        <v>622</v>
+        <v>617</v>
+      </c>
+      <c r="M564" t="n">
+        <v>7</v>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>01:56:50.820</t>
+        </is>
       </c>
       <c r="R564" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>87162</t>
         </is>
       </c>
       <c r="S564" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>133092</t>
         </is>
       </c>
       <c r="Y564" t="inlineStr">
@@ -41040,16 +41162,24 @@
         <v>43</v>
       </c>
       <c r="L565" t="n">
-        <v>623</v>
+        <v>627</v>
+      </c>
+      <c r="M565" t="n">
+        <v>8</v>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>01:56:59.400</t>
+        </is>
       </c>
       <c r="R565" t="inlineStr">
         <is>
-          <t>94211</t>
+          <t>133328</t>
         </is>
       </c>
       <c r="S565" t="inlineStr">
         <is>
-          <t>98352</t>
+          <t>144186</t>
         </is>
       </c>
       <c r="Y565" t="inlineStr">
@@ -41102,23 +41232,31 @@
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="K566" t="n">
         <v>43</v>
       </c>
       <c r="L566" t="n">
-        <v>624</v>
+        <v>626</v>
+      </c>
+      <c r="M566" t="n">
+        <v>9</v>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>01:58:44.340</t>
+        </is>
       </c>
       <c r="R566" t="inlineStr">
         <is>
-          <t>162748</t>
+          <t>147279</t>
         </is>
       </c>
       <c r="S566" t="inlineStr">
         <is>
-          <t>143155</t>
+          <t>154257</t>
         </is>
       </c>
       <c r="Y566" t="inlineStr">
@@ -41171,23 +41309,31 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="K567" t="n">
         <v>43</v>
       </c>
       <c r="L567" t="n">
-        <v>625</v>
+        <v>621</v>
+      </c>
+      <c r="M567" t="n">
+        <v>10</v>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>01:58:45.450</t>
+        </is>
       </c>
       <c r="R567" t="inlineStr">
         <is>
-          <t>64233</t>
+          <t>128714</t>
         </is>
       </c>
       <c r="S567" t="inlineStr">
         <is>
-          <t>128608</t>
+          <t>88900</t>
         </is>
       </c>
       <c r="Y567" t="inlineStr">
@@ -41240,23 +41386,31 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="K568" t="n">
         <v>43</v>
       </c>
       <c r="L568" t="n">
-        <v>626</v>
+        <v>616</v>
+      </c>
+      <c r="M568" t="n">
+        <v>11</v>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>02:00:26.160</t>
+        </is>
       </c>
       <c r="R568" t="inlineStr">
         <is>
-          <t>147279</t>
+          <t>120955</t>
         </is>
       </c>
       <c r="S568" t="inlineStr">
         <is>
-          <t>154257</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="Y568" t="inlineStr">
@@ -41309,23 +41463,31 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="K569" t="n">
         <v>43</v>
       </c>
       <c r="L569" t="n">
-        <v>627</v>
+        <v>624</v>
+      </c>
+      <c r="M569" t="n">
+        <v>12</v>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>02:02:51.640</t>
+        </is>
       </c>
       <c r="R569" t="inlineStr">
         <is>
-          <t>133328</t>
+          <t>162748</t>
         </is>
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>144186</t>
+          <t>143155</t>
         </is>
       </c>
       <c r="Y569" t="inlineStr">
@@ -41387,6 +41549,14 @@
       <c r="L570" t="n">
         <v>628</v>
       </c>
+      <c r="M570" t="n">
+        <v>13</v>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>02:02:56.670</t>
+        </is>
+      </c>
       <c r="R570" t="inlineStr">
         <is>
           <t>97898</t>
@@ -41456,6 +41626,14 @@
       <c r="L571" t="n">
         <v>629</v>
       </c>
+      <c r="M571" t="n">
+        <v>14</v>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>02:07:06.960</t>
+        </is>
+      </c>
       <c r="R571" t="inlineStr">
         <is>
           <t>98391</t>
@@ -41525,6 +41703,14 @@
       <c r="L572" t="n">
         <v>630</v>
       </c>
+      <c r="M572" t="n">
+        <v>15</v>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>02:09:45.680</t>
+        </is>
+      </c>
       <c r="R572" t="inlineStr">
         <is>
           <t>154219</t>
@@ -41594,6 +41780,14 @@
       <c r="L573" t="n">
         <v>631</v>
       </c>
+      <c r="M573" t="n">
+        <v>1</v>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>01:39:38.610</t>
+        </is>
+      </c>
       <c r="R573" t="inlineStr">
         <is>
           <t>48163</t>
@@ -41654,23 +41848,31 @@
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K574" t="n">
         <v>44</v>
       </c>
       <c r="L574" t="n">
-        <v>632</v>
+        <v>634</v>
+      </c>
+      <c r="M574" t="n">
+        <v>2</v>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>01:40:13.320</t>
+        </is>
       </c>
       <c r="R574" t="inlineStr">
         <is>
-          <t>114632</t>
+          <t>76947</t>
         </is>
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>63242</t>
         </is>
       </c>
       <c r="Y574" t="inlineStr">
@@ -41723,23 +41925,31 @@
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="K575" t="n">
         <v>44</v>
       </c>
       <c r="L575" t="n">
-        <v>633</v>
+        <v>637</v>
+      </c>
+      <c r="M575" t="n">
+        <v>3</v>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>01:40:34.330</t>
+        </is>
       </c>
       <c r="R575" t="inlineStr">
         <is>
-          <t>176618</t>
+          <t>63810</t>
         </is>
       </c>
       <c r="S575" t="inlineStr">
         <is>
-          <t>176619</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="Y575" t="inlineStr">
@@ -41792,23 +42002,31 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="K576" t="n">
         <v>44</v>
       </c>
       <c r="L576" t="n">
-        <v>634</v>
+        <v>635</v>
+      </c>
+      <c r="M576" t="n">
+        <v>4</v>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>01:40:51.220</t>
+        </is>
       </c>
       <c r="R576" t="inlineStr">
         <is>
-          <t>76947</t>
+          <t>162143</t>
         </is>
       </c>
       <c r="S576" t="inlineStr">
         <is>
-          <t>63242</t>
+          <t>172054</t>
         </is>
       </c>
       <c r="Y576" t="inlineStr">
@@ -41861,23 +42079,31 @@
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K577" t="n">
         <v>44</v>
       </c>
       <c r="L577" t="n">
-        <v>635</v>
+        <v>636</v>
+      </c>
+      <c r="M577" t="n">
+        <v>5</v>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>01:41:48.930</t>
+        </is>
       </c>
       <c r="R577" t="inlineStr">
         <is>
-          <t>162143</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="S577" t="inlineStr">
         <is>
-          <t>172054</t>
+          <t>46825</t>
         </is>
       </c>
       <c r="Y577" t="inlineStr">
@@ -41930,23 +42156,31 @@
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K578" t="n">
         <v>44</v>
       </c>
       <c r="L578" t="n">
-        <v>636</v>
+        <v>632</v>
+      </c>
+      <c r="M578" t="n">
+        <v>6</v>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>01:42:07.820</t>
+        </is>
       </c>
       <c r="R578" t="inlineStr">
         <is>
-          <t>46822</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="S578" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>105007</t>
         </is>
       </c>
       <c r="Y578" t="inlineStr">
@@ -41999,23 +42233,31 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="K579" t="n">
         <v>44</v>
       </c>
       <c r="L579" t="n">
-        <v>637</v>
+        <v>639</v>
+      </c>
+      <c r="M579" t="n">
+        <v>7</v>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>01:48:52.100</t>
+        </is>
       </c>
       <c r="R579" t="inlineStr">
         <is>
-          <t>63810</t>
+          <t>168283</t>
         </is>
       </c>
       <c r="S579" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>168335</t>
         </is>
       </c>
       <c r="Y579" t="inlineStr">
@@ -42075,16 +42317,24 @@
         <v>44</v>
       </c>
       <c r="L580" t="n">
-        <v>638</v>
+        <v>633</v>
+      </c>
+      <c r="M580" t="n">
+        <v>8</v>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>02:07:29.070</t>
+        </is>
       </c>
       <c r="R580" t="inlineStr">
         <is>
-          <t>176774</t>
+          <t>176618</t>
         </is>
       </c>
       <c r="S580" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>176619</t>
         </is>
       </c>
       <c r="Y580" t="inlineStr">
@@ -42137,23 +42387,31 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="K581" t="n">
         <v>44</v>
       </c>
       <c r="L581" t="n">
-        <v>639</v>
+        <v>638</v>
+      </c>
+      <c r="M581" t="n">
+        <v>9</v>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>01:49:43.830</t>
+        </is>
       </c>
       <c r="R581" t="inlineStr">
         <is>
-          <t>168283</t>
+          <t>176774</t>
         </is>
       </c>
       <c r="S581" t="inlineStr">
         <is>
-          <t>168335</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="Y581" t="inlineStr">
@@ -42206,23 +42464,31 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="K582" t="n">
         <v>45</v>
       </c>
       <c r="L582" t="n">
-        <v>641</v>
+        <v>650</v>
+      </c>
+      <c r="M582" t="n">
+        <v>1</v>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>01:33:10.330</t>
+        </is>
       </c>
       <c r="R582" t="inlineStr">
         <is>
-          <t>178007</t>
+          <t>149673</t>
         </is>
       </c>
       <c r="S582" t="inlineStr">
         <is>
-          <t>178008</t>
+          <t>135238</t>
         </is>
       </c>
       <c r="Y582" t="inlineStr">
@@ -42275,23 +42541,31 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K583" t="n">
         <v>45</v>
       </c>
       <c r="L583" t="n">
-        <v>642</v>
+        <v>655</v>
+      </c>
+      <c r="M583" t="n">
+        <v>2</v>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>01:33:18.470</t>
+        </is>
       </c>
       <c r="R583" t="inlineStr">
         <is>
-          <t>168273</t>
+          <t>160392</t>
         </is>
       </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>168274</t>
+          <t>156104</t>
         </is>
       </c>
       <c r="Y583" t="inlineStr">
@@ -42344,23 +42618,31 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>URU</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K584" t="n">
         <v>45</v>
       </c>
       <c r="L584" t="n">
-        <v>644</v>
+        <v>652</v>
+      </c>
+      <c r="M584" t="n">
+        <v>3</v>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>01:33:29.220</t>
+        </is>
       </c>
       <c r="R584" t="inlineStr">
         <is>
-          <t>178001</t>
+          <t>156093</t>
         </is>
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>160337</t>
+          <t>156092</t>
         </is>
       </c>
       <c r="Y584" t="inlineStr">
@@ -42413,23 +42695,31 @@
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="K585" t="n">
         <v>45</v>
       </c>
       <c r="L585" t="n">
-        <v>645</v>
+        <v>656</v>
+      </c>
+      <c r="M585" t="n">
+        <v>4</v>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>01:35:32.420</t>
+        </is>
       </c>
       <c r="R585" t="inlineStr">
         <is>
-          <t>176626</t>
+          <t>155917</t>
         </is>
       </c>
       <c r="S585" t="inlineStr">
         <is>
-          <t>176627</t>
+          <t>136699</t>
         </is>
       </c>
       <c r="Y585" t="inlineStr">
@@ -42482,23 +42772,31 @@
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="K586" t="n">
         <v>45</v>
       </c>
       <c r="L586" t="n">
-        <v>646</v>
+        <v>657</v>
+      </c>
+      <c r="M586" t="n">
+        <v>5</v>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>01:36:28.170</t>
+        </is>
       </c>
       <c r="R586" t="inlineStr">
         <is>
-          <t>159003</t>
+          <t>160451</t>
         </is>
       </c>
       <c r="S586" t="inlineStr">
         <is>
-          <t>143639</t>
+          <t>149150</t>
         </is>
       </c>
       <c r="Y586" t="inlineStr">
@@ -42551,23 +42849,31 @@
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="K587" t="n">
         <v>45</v>
       </c>
       <c r="L587" t="n">
-        <v>647</v>
+        <v>648</v>
+      </c>
+      <c r="M587" t="n">
+        <v>6</v>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>01:36:36.310</t>
+        </is>
       </c>
       <c r="R587" t="inlineStr">
         <is>
-          <t>171772</t>
+          <t>168015</t>
         </is>
       </c>
       <c r="S587" t="inlineStr">
         <is>
-          <t>171774</t>
+          <t>168014</t>
         </is>
       </c>
       <c r="Y587" t="inlineStr">
@@ -42620,23 +42926,31 @@
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K588" t="n">
         <v>45</v>
       </c>
       <c r="L588" t="n">
-        <v>648</v>
+        <v>642</v>
+      </c>
+      <c r="M588" t="n">
+        <v>7</v>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>01:36:45.010</t>
+        </is>
       </c>
       <c r="R588" t="inlineStr">
         <is>
-          <t>168015</t>
+          <t>168273</t>
         </is>
       </c>
       <c r="S588" t="inlineStr">
         <is>
-          <t>168014</t>
+          <t>168274</t>
         </is>
       </c>
       <c r="Y588" t="inlineStr">
@@ -42689,23 +43003,31 @@
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="K589" t="n">
         <v>45</v>
       </c>
       <c r="L589" t="n">
-        <v>649</v>
+        <v>654</v>
+      </c>
+      <c r="M589" t="n">
+        <v>8</v>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>01:36:49.120</t>
+        </is>
       </c>
       <c r="R589" t="inlineStr">
         <is>
-          <t>160453</t>
+          <t>131143</t>
         </is>
       </c>
       <c r="S589" t="inlineStr">
         <is>
-          <t>176773</t>
+          <t>131144</t>
         </is>
       </c>
       <c r="Y589" t="inlineStr">
@@ -42758,23 +43080,31 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>URU</t>
         </is>
       </c>
       <c r="K590" t="n">
         <v>45</v>
       </c>
       <c r="L590" t="n">
-        <v>650</v>
+        <v>644</v>
+      </c>
+      <c r="M590" t="n">
+        <v>9</v>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>01:38:53.450</t>
+        </is>
       </c>
       <c r="R590" t="inlineStr">
         <is>
-          <t>149673</t>
+          <t>178001</t>
         </is>
       </c>
       <c r="S590" t="inlineStr">
         <is>
-          <t>135238</t>
+          <t>160337</t>
         </is>
       </c>
       <c r="Y590" t="inlineStr">
@@ -42827,23 +43157,31 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="K591" t="n">
         <v>45</v>
       </c>
       <c r="L591" t="n">
-        <v>651</v>
+        <v>653</v>
+      </c>
+      <c r="M591" t="n">
+        <v>10</v>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>01:38:56.220</t>
+        </is>
       </c>
       <c r="R591" t="inlineStr">
         <is>
-          <t>155048</t>
+          <t>131172</t>
         </is>
       </c>
       <c r="S591" t="inlineStr">
         <is>
-          <t>159019</t>
+          <t>166734</t>
         </is>
       </c>
       <c r="Y591" t="inlineStr">
@@ -42896,23 +43234,31 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K592" t="n">
         <v>45</v>
       </c>
       <c r="L592" t="n">
-        <v>652</v>
+        <v>651</v>
+      </c>
+      <c r="M592" t="n">
+        <v>11</v>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>01:39:35.090</t>
+        </is>
       </c>
       <c r="R592" t="inlineStr">
         <is>
-          <t>156093</t>
+          <t>155048</t>
         </is>
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>156092</t>
+          <t>159019</t>
         </is>
       </c>
       <c r="Y592" t="inlineStr">
@@ -42965,23 +43311,31 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="K593" t="n">
         <v>45</v>
       </c>
       <c r="L593" t="n">
-        <v>653</v>
+        <v>649</v>
+      </c>
+      <c r="M593" t="n">
+        <v>12</v>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>01:42:25.330</t>
+        </is>
       </c>
       <c r="R593" t="inlineStr">
         <is>
-          <t>131172</t>
+          <t>160453</t>
         </is>
       </c>
       <c r="S593" t="inlineStr">
         <is>
-          <t>166734</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="Y593" t="inlineStr">
@@ -43034,23 +43388,31 @@
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>RSA</t>
         </is>
       </c>
       <c r="K594" t="n">
         <v>45</v>
       </c>
       <c r="L594" t="n">
-        <v>654</v>
+        <v>647</v>
+      </c>
+      <c r="M594" t="n">
+        <v>13</v>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>01:42:31.920</t>
+        </is>
       </c>
       <c r="R594" t="inlineStr">
         <is>
-          <t>131143</t>
+          <t>171772</t>
         </is>
       </c>
       <c r="S594" t="inlineStr">
         <is>
-          <t>131144</t>
+          <t>171774</t>
         </is>
       </c>
       <c r="Y594" t="inlineStr">
@@ -43103,23 +43465,31 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="K595" t="n">
         <v>45</v>
       </c>
       <c r="L595" t="n">
-        <v>655</v>
+        <v>645</v>
+      </c>
+      <c r="M595" t="n">
+        <v>14</v>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>01:44:33.030</t>
+        </is>
       </c>
       <c r="R595" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>176626</t>
         </is>
       </c>
       <c r="S595" t="inlineStr">
         <is>
-          <t>156104</t>
+          <t>176627</t>
         </is>
       </c>
       <c r="Y595" t="inlineStr">
@@ -43172,23 +43542,28 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="K596" t="n">
         <v>45</v>
       </c>
       <c r="L596" t="n">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="R596" t="inlineStr">
         <is>
-          <t>155917</t>
+          <t>159003</t>
         </is>
       </c>
       <c r="S596" t="inlineStr">
         <is>
-          <t>136699</t>
+          <t>143639</t>
+        </is>
+      </c>
+      <c r="X596" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
       <c r="Y596" t="inlineStr">
@@ -43241,23 +43616,28 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="K597" t="n">
         <v>45</v>
       </c>
       <c r="L597" t="n">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>160451</t>
+          <t>178007</t>
         </is>
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>149150</t>
+          <t>178008</t>
+        </is>
+      </c>
+      <c r="X597" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
       <c r="Y597" t="inlineStr">
@@ -43310,23 +43690,31 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="K598" t="n">
         <v>46</v>
       </c>
       <c r="L598" t="n">
-        <v>661</v>
+        <v>666</v>
+      </c>
+      <c r="M598" t="n">
+        <v>1</v>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>01:58:08.980</t>
+        </is>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>104234</t>
+          <t>113662</t>
         </is>
       </c>
       <c r="S598" t="inlineStr">
         <is>
-          <t>73771</t>
+          <t>42846</t>
         </is>
       </c>
       <c r="Y598" t="inlineStr">
@@ -43379,23 +43767,31 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="K599" t="n">
         <v>46</v>
       </c>
       <c r="L599" t="n">
-        <v>662</v>
+        <v>664</v>
+      </c>
+      <c r="M599" t="n">
+        <v>2</v>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>01:58:10.730</t>
+        </is>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>113656</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="Y599" t="inlineStr">
@@ -43448,23 +43844,31 @@
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K600" t="n">
         <v>46</v>
       </c>
       <c r="L600" t="n">
-        <v>663</v>
+        <v>677</v>
+      </c>
+      <c r="M600" t="n">
+        <v>3</v>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>01:58:21.100</t>
+        </is>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="S600" t="inlineStr">
         <is>
-          <t>132627</t>
+          <t>88713</t>
         </is>
       </c>
       <c r="Y600" t="inlineStr">
@@ -43517,23 +43921,31 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="K601" t="n">
         <v>46</v>
       </c>
       <c r="L601" t="n">
-        <v>664</v>
+        <v>669</v>
+      </c>
+      <c r="M601" t="n">
+        <v>4</v>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>01:58:22.620</t>
+        </is>
       </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>98874</t>
         </is>
       </c>
       <c r="S601" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>72618</t>
         </is>
       </c>
       <c r="Y601" t="inlineStr">
@@ -43586,23 +43998,31 @@
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="K602" t="n">
         <v>46</v>
       </c>
       <c r="L602" t="n">
-        <v>665</v>
+        <v>662</v>
+      </c>
+      <c r="M602" t="n">
+        <v>5</v>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>01:58:33.310</t>
+        </is>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="S602" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>113656</t>
         </is>
       </c>
       <c r="Y602" t="inlineStr">
@@ -43655,23 +44075,31 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="K603" t="n">
         <v>46</v>
       </c>
       <c r="L603" t="n">
-        <v>666</v>
+        <v>668</v>
+      </c>
+      <c r="M603" t="n">
+        <v>6</v>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>01:58:39.160</t>
+        </is>
       </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>113662</t>
+          <t>53158</t>
         </is>
       </c>
       <c r="S603" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>161538</t>
         </is>
       </c>
       <c r="Y603" t="inlineStr">
@@ -43724,23 +44152,31 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="K604" t="n">
         <v>46</v>
       </c>
       <c r="L604" t="n">
-        <v>667</v>
+        <v>665</v>
+      </c>
+      <c r="M604" t="n">
+        <v>7</v>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>01:58:46.060</t>
+        </is>
       </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>135253</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="S604" t="inlineStr">
         <is>
-          <t>135807</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="Y604" t="inlineStr">
@@ -43793,23 +44229,31 @@
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K605" t="n">
         <v>46</v>
       </c>
       <c r="L605" t="n">
-        <v>668</v>
+        <v>678</v>
+      </c>
+      <c r="M605" t="n">
+        <v>8</v>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>02:00:13.700</t>
+        </is>
       </c>
       <c r="R605" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>104881</t>
         </is>
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>161538</t>
+          <t>105015</t>
         </is>
       </c>
       <c r="Y605" t="inlineStr">
@@ -43869,16 +44313,24 @@
         <v>46</v>
       </c>
       <c r="L606" t="n">
-        <v>669</v>
+        <v>673</v>
+      </c>
+      <c r="M606" t="n">
+        <v>9</v>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>02:01:09.740</t>
+        </is>
       </c>
       <c r="R606" t="inlineStr">
         <is>
-          <t>98874</t>
+          <t>112062</t>
         </is>
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>72618</t>
+          <t>176768</t>
         </is>
       </c>
       <c r="Y606" t="inlineStr">
@@ -43931,23 +44383,31 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>RSA</t>
         </is>
       </c>
       <c r="K607" t="n">
         <v>46</v>
       </c>
       <c r="L607" t="n">
-        <v>670</v>
+        <v>675</v>
+      </c>
+      <c r="M607" t="n">
+        <v>10</v>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>02:01:10.600</t>
+        </is>
       </c>
       <c r="R607" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>81201</t>
         </is>
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>95939</t>
+          <t>147774</t>
         </is>
       </c>
       <c r="Y607" t="inlineStr">
@@ -44000,23 +44460,31 @@
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="K608" t="n">
         <v>46</v>
       </c>
       <c r="L608" t="n">
-        <v>671</v>
+        <v>667</v>
+      </c>
+      <c r="M608" t="n">
+        <v>11</v>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>02:01:10.710</t>
+        </is>
       </c>
       <c r="R608" t="inlineStr">
         <is>
-          <t>128713</t>
+          <t>135253</t>
         </is>
       </c>
       <c r="S608" t="inlineStr">
         <is>
-          <t>128710</t>
+          <t>135807</t>
         </is>
       </c>
       <c r="Y608" t="inlineStr">
@@ -44069,23 +44537,31 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>URU</t>
+          <t>RSA</t>
         </is>
       </c>
       <c r="K609" t="n">
         <v>46</v>
       </c>
       <c r="L609" t="n">
-        <v>672</v>
+        <v>661</v>
+      </c>
+      <c r="M609" t="n">
+        <v>12</v>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>02:01:11.000</t>
+        </is>
       </c>
       <c r="R609" t="inlineStr">
         <is>
-          <t>113735</t>
+          <t>104234</t>
         </is>
       </c>
       <c r="S609" t="inlineStr">
         <is>
-          <t>178003</t>
+          <t>73771</t>
         </is>
       </c>
       <c r="Y609" t="inlineStr">
@@ -44138,23 +44614,31 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="K610" t="n">
         <v>46</v>
       </c>
       <c r="L610" t="n">
-        <v>673</v>
+        <v>679</v>
+      </c>
+      <c r="M610" t="n">
+        <v>13</v>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>02:02:59.720</t>
+        </is>
       </c>
       <c r="R610" t="inlineStr">
         <is>
-          <t>112062</t>
+          <t>102756</t>
         </is>
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>176768</t>
+          <t>110882</t>
         </is>
       </c>
       <c r="Y610" t="inlineStr">
@@ -44207,23 +44691,31 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="K611" t="n">
         <v>46</v>
       </c>
       <c r="L611" t="n">
-        <v>674</v>
+        <v>671</v>
+      </c>
+      <c r="M611" t="n">
+        <v>14</v>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>02:03:26.890</t>
+        </is>
       </c>
       <c r="R611" t="inlineStr">
         <is>
-          <t>178015</t>
+          <t>128713</t>
         </is>
       </c>
       <c r="S611" t="inlineStr">
         <is>
-          <t>178014</t>
+          <t>128710</t>
         </is>
       </c>
       <c r="Y611" t="inlineStr">
@@ -44276,23 +44768,31 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="K612" t="n">
         <v>46</v>
       </c>
       <c r="L612" t="n">
-        <v>675</v>
+        <v>663</v>
+      </c>
+      <c r="M612" t="n">
+        <v>15</v>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>02:04:34.650</t>
+        </is>
       </c>
       <c r="R612" t="inlineStr">
         <is>
-          <t>81201</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="S612" t="inlineStr">
         <is>
-          <t>147774</t>
+          <t>132627</t>
         </is>
       </c>
       <c r="Y612" t="inlineStr">
@@ -44345,23 +44845,31 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>URU</t>
         </is>
       </c>
       <c r="K613" t="n">
         <v>46</v>
       </c>
       <c r="L613" t="n">
-        <v>677</v>
+        <v>672</v>
+      </c>
+      <c r="M613" t="n">
+        <v>16</v>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>02:09:15.040</t>
+        </is>
       </c>
       <c r="R613" t="inlineStr">
         <is>
-          <t>49663</t>
+          <t>113735</t>
         </is>
       </c>
       <c r="S613" t="inlineStr">
         <is>
-          <t>88713</t>
+          <t>178003</t>
         </is>
       </c>
       <c r="Y613" t="inlineStr">
@@ -44414,23 +44922,31 @@
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="K614" t="n">
         <v>46</v>
       </c>
       <c r="L614" t="n">
-        <v>678</v>
+        <v>680</v>
+      </c>
+      <c r="M614" t="n">
+        <v>17</v>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>02:12:40.910</t>
+        </is>
       </c>
       <c r="R614" t="inlineStr">
         <is>
-          <t>104881</t>
+          <t>125088</t>
         </is>
       </c>
       <c r="S614" t="inlineStr">
         <is>
-          <t>105015</t>
+          <t>125087</t>
         </is>
       </c>
       <c r="Y614" t="inlineStr">
@@ -44483,23 +44999,31 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="K615" t="n">
         <v>46</v>
       </c>
       <c r="L615" t="n">
-        <v>679</v>
+        <v>674</v>
+      </c>
+      <c r="M615" t="n">
+        <v>18</v>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>01:59:55.950</t>
+        </is>
       </c>
       <c r="R615" t="inlineStr">
         <is>
-          <t>102756</t>
+          <t>178015</t>
         </is>
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>110882</t>
+          <t>178014</t>
         </is>
       </c>
       <c r="Y615" t="inlineStr">
@@ -44552,23 +45076,31 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="K616" t="n">
         <v>46</v>
       </c>
       <c r="L616" t="n">
-        <v>680</v>
+        <v>681</v>
+      </c>
+      <c r="M616" t="n">
+        <v>18</v>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>02:07:27.740</t>
+        </is>
       </c>
       <c r="R616" t="inlineStr">
         <is>
-          <t>125088</t>
+          <t>133098</t>
         </is>
       </c>
       <c r="S616" t="inlineStr">
         <is>
-          <t>125087</t>
+          <t>152144</t>
         </is>
       </c>
       <c r="Y616" t="inlineStr">
@@ -44621,23 +45153,31 @@
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="K617" t="n">
         <v>46</v>
       </c>
       <c r="L617" t="n">
-        <v>681</v>
+        <v>683</v>
+      </c>
+      <c r="M617" t="n">
+        <v>18</v>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>02:10:11.540</t>
+        </is>
       </c>
       <c r="R617" t="inlineStr">
         <is>
-          <t>133098</t>
+          <t>178010</t>
         </is>
       </c>
       <c r="S617" t="inlineStr">
         <is>
-          <t>152144</t>
+          <t>178009</t>
         </is>
       </c>
       <c r="Y617" t="inlineStr">
@@ -44690,23 +45230,28 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="K618" t="n">
         <v>46</v>
       </c>
       <c r="L618" t="n">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="R618" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="S618" t="inlineStr">
         <is>
-          <t>88547</t>
+          <t>95939</t>
+        </is>
+      </c>
+      <c r="X618" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
       <c r="Y618" t="inlineStr">
@@ -44759,23 +45304,28 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="K619" t="n">
         <v>46</v>
       </c>
       <c r="L619" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="R619" t="inlineStr">
         <is>
-          <t>178010</t>
+          <t>87308</t>
         </is>
       </c>
       <c r="S619" t="inlineStr">
         <is>
-          <t>178009</t>
+          <t>88547</t>
+        </is>
+      </c>
+      <c r="X619" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
       <c r="Y619" t="inlineStr">
